--- a/config/report_requirenment.xlsx
+++ b/config/report_requirenment.xlsx
@@ -17,7 +17,7 @@
     <sheet name="参考文献匹配规则" sheetId="12" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">report_requirenment!$A$1:$P$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">report_requirenment!$A$1:$P$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'reference-fixed'!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="396">
   <si>
     <t>产品名称</t>
   </si>
@@ -628,6 +628,27 @@
   </si>
   <si>
     <t>tOncoPro_XW6701_3gene_v1.0.docx</t>
+  </si>
+  <si>
+    <t>2025.12.23</t>
+  </si>
+  <si>
+    <t>BG（组织）</t>
+  </si>
+  <si>
+    <t>XW4303-BG</t>
+  </si>
+  <si>
+    <t>tOncoPro_XW4303_v2.0.docx</t>
+  </si>
+  <si>
+    <t>MRD（LC10）</t>
+  </si>
+  <si>
+    <t>MRD_v1.4.docx</t>
+  </si>
+  <si>
+    <t>2026.01.29</t>
   </si>
   <si>
     <t>docx_template</t>
@@ -1492,12 +1513,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2521,7 +2542,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P86"/>
+  <dimension ref="A1:P89"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -5725,18 +5746,123 @@
         <v>143</v>
       </c>
     </row>
+    <row r="87" customFormat="1" spans="1:15">
+      <c r="A87" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="B87" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="C87" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D87" t="s">
+        <v>153</v>
+      </c>
+      <c r="E87" s="36"/>
+      <c r="F87" s="36"/>
+      <c r="G87" s="36" t="s">
+        <v>167</v>
+      </c>
+      <c r="H87" s="36">
+        <v>0</v>
+      </c>
+      <c r="I87" s="36">
+        <v>1</v>
+      </c>
+      <c r="J87" s="36"/>
+      <c r="K87" s="36"/>
+      <c r="L87" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="M87" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="N87" t="s">
+        <v>171</v>
+      </c>
+      <c r="O87" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15">
+      <c r="A88" t="s">
+        <v>172</v>
+      </c>
+      <c r="B88" t="s">
+        <v>173</v>
+      </c>
+      <c r="C88" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D88" t="s">
+        <v>153</v>
+      </c>
+      <c r="G88" t="s">
+        <v>174</v>
+      </c>
+      <c r="H88" s="36">
+        <v>0</v>
+      </c>
+      <c r="I88" s="36">
+        <v>1</v>
+      </c>
+      <c r="J88" s="36"/>
+      <c r="K88" s="36"/>
+      <c r="L88" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="M88" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="N88" t="s">
+        <v>171</v>
+      </c>
+      <c r="O88" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="89" customFormat="1" spans="1:15">
+      <c r="A89" t="s">
+        <v>175</v>
+      </c>
+      <c r="C89" t="s">
+        <v>18</v>
+      </c>
+      <c r="D89" t="s">
+        <v>153</v>
+      </c>
+      <c r="G89" t="s">
+        <v>176</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>1</v>
+      </c>
+      <c r="L89" t="s">
+        <v>41</v>
+      </c>
+      <c r="M89" t="s">
+        <v>41</v>
+      </c>
+      <c r="N89" t="s">
+        <v>177</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:P86" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:P88" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1 H2:I80 H87:I1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1 H2:I80 H89:I1048576">
       <formula1>"0,1"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A80 A87:A1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A80 A88:A1048576">
       <formula1>prod_name!$A:$A</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C80 C87:C1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C80 C89:C1048576">
       <formula1>"临检,进院"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D80 D87:D1048576">
@@ -5771,37 +5897,37 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="B1" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C1" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="D1" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="E1" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="F1" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="K1" s="30" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -5827,266 +5953,266 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B2" s="29">
         <v>105</v>
       </c>
       <c r="C2" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B3" s="29">
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B4" s="29">
         <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B5" s="29">
         <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B6" s="29">
         <v>150</v>
       </c>
       <c r="C6" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B7" s="29">
         <v>150</v>
       </c>
       <c r="C7" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B8" s="29">
         <v>150</v>
       </c>
       <c r="C8" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B9" s="29">
         <v>180</v>
       </c>
       <c r="C9" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B10" s="29">
         <v>180</v>
       </c>
       <c r="C10" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B11" s="29">
         <v>180</v>
       </c>
       <c r="C11" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="B12" s="29">
         <v>180</v>
       </c>
       <c r="C12" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B13" s="29">
         <v>180</v>
       </c>
       <c r="C13" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="B14" s="29">
         <v>180</v>
       </c>
       <c r="C14" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B15" s="29">
         <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B16" s="29">
         <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B17" s="29">
         <v>120</v>
       </c>
       <c r="C17" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B18" s="29">
         <v>120</v>
       </c>
       <c r="C18" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B19" s="29">
         <v>120</v>
       </c>
       <c r="C19" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B20" s="29">
         <v>150</v>
       </c>
       <c r="C20" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B21" s="29">
         <v>150</v>
       </c>
       <c r="C21" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B22" s="29">
         <v>150</v>
       </c>
       <c r="C22" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="B23" s="29">
         <v>150</v>
       </c>
       <c r="C23" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B24" s="29">
         <v>150</v>
       </c>
       <c r="C24" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -6107,15 +6233,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="28" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>24</v>
@@ -6123,7 +6249,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="B3" t="s">
         <v>85</v>
@@ -6131,7 +6257,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="B4" t="s">
         <v>85</v>
@@ -6139,111 +6265,111 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="28" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="28" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="28" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="28" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="28" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="28" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="28" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="28" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="28" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="28" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="28" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="28" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B17" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="28" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>63</v>
@@ -6251,7 +6377,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="28" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B19" s="28" t="s">
         <v>63</v>
@@ -6259,15 +6385,15 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="28" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="28" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B21" t="s">
         <v>85</v>
@@ -6275,23 +6401,23 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="28" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="28" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B24" t="s">
         <v>157</v>
@@ -6299,7 +6425,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="28" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B25" s="28" t="s">
         <v>36</v>
@@ -6307,18 +6433,18 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="28" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="28" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -6331,7 +6457,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A61"/>
+  <dimension ref="A1:A62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="29.8333333333333" customWidth="1"/>
@@ -6350,37 +6476,37 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -6390,17 +6516,17 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -6410,12 +6536,12 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -6430,77 +6556,77 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -6510,42 +6636,42 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="26" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="43" spans="1:1">
@@ -6555,17 +6681,17 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
     </row>
     <row r="47" spans="1:1">
@@ -6641,6 +6767,11 @@
     <row r="61" spans="1:1">
       <c r="A61" t="s">
         <v>105</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -6668,7 +6799,7 @@
   <sheetData>
     <row r="2" spans="1:2">
       <c r="A2" s="17" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -6676,7 +6807,7 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -6684,15 +6815,15 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="18" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B5" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -6700,7 +6831,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -6708,7 +6839,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -6716,7 +6847,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -6724,7 +6855,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -6732,7 +6863,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -6740,7 +6871,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -6748,7 +6879,7 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6756,25 +6887,25 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="18" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B14" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="19" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -6785,7 +6916,7 @@
         <v>2</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>4</v>
@@ -6812,7 +6943,7 @@
         <v>14</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
     </row>
     <row r="18" ht="15.5" spans="1:12">
@@ -6826,26 +6957,26 @@
         <v>19</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="G18" s="3">
         <v>0</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="L18" s="3"/>
     </row>
@@ -6862,22 +6993,22 @@
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="G19" s="3">
         <v>0</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="L19" s="3"/>
     </row>
@@ -6889,27 +7020,27 @@
         <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="L20" s="3"/>
     </row>
@@ -6924,28 +7055,28 @@
         <v>19</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>323</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>316</v>
       </c>
       <c r="L21" s="3"/>
     </row>
@@ -6957,61 +7088,61 @@
         <v>148</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="L22" s="3"/>
     </row>
     <row r="25" ht="15.5" spans="1:12">
       <c r="A25" s="23" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
     </row>
     <row r="26" ht="15.5" spans="1:12">
       <c r="A26" s="24" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
     </row>
     <row r="27" ht="15.5" spans="1:12">
       <c r="A27" s="23" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="B27" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
     </row>
     <row r="28" ht="15.5" spans="1:12">
       <c r="A28" s="23" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B28" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
     </row>
     <row r="29" ht="15.5" spans="1:12">
       <c r="A29" s="25" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B29" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
     </row>
     <row r="30" ht="15.5" spans="1:12">
@@ -7019,7 +7150,7 @@
         <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -7048,16 +7179,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="13" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>14</v>
@@ -7068,78 +7199,78 @@
         <v>19</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="15"/>
       <c r="B3" s="3" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="14" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="16"/>
       <c r="B5" s="3" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="15"/>
       <c r="B6" s="3" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -7161,79 +7292,79 @@
   <sheetData>
     <row r="5" spans="3:6">
       <c r="C5" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="D5" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7" spans="3:6">
       <c r="C7" s="1" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8" spans="3:6">
       <c r="C8" s="2" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
     <row r="9" spans="3:6">
       <c r="C9" s="2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="3:6">
       <c r="C10" s="4" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="11" spans="3:6">
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="3" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
     </row>
     <row r="12" spans="3:6">
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="3" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
     </row>
     <row r="13" spans="3:6">
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="3" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
     <row r="14" spans="3:6">
@@ -7244,23 +7375,23 @@
     </row>
     <row r="15" spans="3:6">
       <c r="C15" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
     </row>
     <row r="16" spans="3:6">
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="3" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="F16" s="3"/>
     </row>
@@ -7268,7 +7399,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="3" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="F17" s="3"/>
     </row>
@@ -7276,7 +7407,7 @@
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="3" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="F18" s="3"/>
     </row>
@@ -7284,7 +7415,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="3" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="F19" s="3"/>
     </row>
@@ -7292,19 +7423,19 @@
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="3" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="F20" s="3"/>
     </row>
     <row r="21" spans="3:6">
       <c r="C21" s="4" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="F21" s="3"/>
     </row>
@@ -7312,7 +7443,7 @@
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="3" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="F22" s="3"/>
     </row>
@@ -7320,13 +7451,13 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="3" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="F23" s="3"/>
     </row>
     <row r="24" spans="3:6">
       <c r="C24" s="3" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>14</v>
@@ -7336,17 +7467,17 @@
     </row>
     <row r="25" spans="3:6">
       <c r="C25" s="3" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
     </row>
     <row r="26" spans="3:6">
       <c r="C26" s="3" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="3"/>
@@ -7354,7 +7485,7 @@
     </row>
     <row r="27" spans="3:6">
       <c r="C27" s="3" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="D27" s="7"/>
       <c r="E27" s="3"/>
@@ -7362,7 +7493,7 @@
     </row>
     <row r="28" spans="3:6">
       <c r="C28" s="3" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="3"/>
@@ -7370,7 +7501,7 @@
     </row>
     <row r="29" spans="3:6">
       <c r="C29" s="3" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="3"/>
@@ -7378,19 +7509,19 @@
     </row>
     <row r="35" spans="3:6">
       <c r="C35" s="9" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="F35" s="9"/>
     </row>
     <row r="36" spans="3:6">
       <c r="C36" s="11" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
@@ -7398,29 +7529,29 @@
     </row>
     <row r="37" spans="3:6">
       <c r="C37" s="12" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="E37" s="12"/>
       <c r="F37" s="9"/>
     </row>
     <row r="38" spans="3:6">
       <c r="C38" s="12" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="F38" s="9"/>
     </row>
     <row r="39" spans="3:6">
       <c r="C39" s="12" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="D39" s="12" t="s">
         <v>14</v>

--- a/config/report_requirenment.xlsx
+++ b/config/report_requirenment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12280"/>
+    <workbookView windowWidth="19200" windowHeight="6880"/>
   </bookViews>
   <sheets>
     <sheet name="report_requirenment" sheetId="2" r:id="rId1"/>
@@ -17,7 +17,7 @@
     <sheet name="参考文献匹配规则" sheetId="12" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">report_requirenment!$A$1:$P$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">report_requirenment!$A$1:$P$95</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'reference-fixed'!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="414">
   <si>
     <t>产品名称</t>
   </si>
@@ -649,6 +649,60 @@
   </si>
   <si>
     <t>2026.01.29</t>
+  </si>
+  <si>
+    <t>tOncoPro_XW4303_v3.0.docx</t>
+  </si>
+  <si>
+    <t>2026.03.17</t>
+  </si>
+  <si>
+    <t>CP200（组织）</t>
+  </si>
+  <si>
+    <t>XW4221-Oncopro200</t>
+  </si>
+  <si>
+    <t>tOncoPro_XW4221_v1.0.docx</t>
+  </si>
+  <si>
+    <t>2026.04.15</t>
+  </si>
+  <si>
+    <t>XW7201-Master Panel（血液）</t>
+  </si>
+  <si>
+    <t>MasterBlood_XW7201_v1.0.docx</t>
+  </si>
+  <si>
+    <t>XW4217-10基因组织</t>
+  </si>
+  <si>
+    <t>tLC10_XW4217_v2.0.docx</t>
+  </si>
+  <si>
+    <t>XW4217-10基因血液</t>
+  </si>
+  <si>
+    <t>gLC10_XW4217_v2.0.docx</t>
+  </si>
+  <si>
+    <t>XW8003-HRD complete</t>
+  </si>
+  <si>
+    <t>tHRD_XW8003_v1.0.docx</t>
+  </si>
+  <si>
+    <t>2026.04.16</t>
+  </si>
+  <si>
+    <t>XW5303-Oncopro200</t>
+  </si>
+  <si>
+    <t>tOncoPro_XW5303_v1.0.docx</t>
+  </si>
+  <si>
+    <t>2026.04.28</t>
   </si>
   <si>
     <t>docx_template</t>
@@ -1513,12 +1567,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2542,7 +2596,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P89"/>
+  <dimension ref="A1:P96"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -5851,21 +5905,259 @@
         <v>177</v>
       </c>
     </row>
+    <row r="90" spans="1:15">
+      <c r="A90" t="s">
+        <v>172</v>
+      </c>
+      <c r="B90" t="s">
+        <v>173</v>
+      </c>
+      <c r="C90" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D90" t="s">
+        <v>153</v>
+      </c>
+      <c r="G90" t="s">
+        <v>178</v>
+      </c>
+      <c r="H90" s="36">
+        <v>0</v>
+      </c>
+      <c r="I90" s="36">
+        <v>1</v>
+      </c>
+      <c r="J90" s="36"/>
+      <c r="K90" s="36"/>
+      <c r="L90" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="M90" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="N90" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15">
+      <c r="A91" t="s">
+        <v>180</v>
+      </c>
+      <c r="B91" t="s">
+        <v>181</v>
+      </c>
+      <c r="C91" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D91" t="s">
+        <v>153</v>
+      </c>
+      <c r="G91" t="s">
+        <v>182</v>
+      </c>
+      <c r="H91" s="36">
+        <v>0</v>
+      </c>
+      <c r="I91" s="36">
+        <v>1</v>
+      </c>
+      <c r="J91" s="36"/>
+      <c r="K91" s="36"/>
+      <c r="L91" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="M91" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="N91" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15">
+      <c r="A92" t="s">
+        <v>67</v>
+      </c>
+      <c r="B92" t="s">
+        <v>184</v>
+      </c>
+      <c r="C92" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D92" t="s">
+        <v>153</v>
+      </c>
+      <c r="G92" t="s">
+        <v>185</v>
+      </c>
+      <c r="H92" s="36">
+        <v>0</v>
+      </c>
+      <c r="I92" s="36">
+        <v>1</v>
+      </c>
+      <c r="J92" s="36"/>
+      <c r="K92" s="36"/>
+      <c r="L92" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="M92" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="N92" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15">
+      <c r="A93" t="s">
+        <v>85</v>
+      </c>
+      <c r="B93" t="s">
+        <v>186</v>
+      </c>
+      <c r="C93" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D93" t="s">
+        <v>153</v>
+      </c>
+      <c r="G93" t="s">
+        <v>187</v>
+      </c>
+      <c r="H93" s="36">
+        <v>0</v>
+      </c>
+      <c r="I93" s="36">
+        <v>1</v>
+      </c>
+      <c r="J93" s="36"/>
+      <c r="K93" s="36"/>
+      <c r="L93" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="M93" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="N93" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15">
+      <c r="A94" t="s">
+        <v>24</v>
+      </c>
+      <c r="B94" t="s">
+        <v>188</v>
+      </c>
+      <c r="C94" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D94" t="s">
+        <v>153</v>
+      </c>
+      <c r="G94" t="s">
+        <v>189</v>
+      </c>
+      <c r="H94" s="36">
+        <v>0</v>
+      </c>
+      <c r="I94" s="36">
+        <v>1</v>
+      </c>
+      <c r="J94" s="36"/>
+      <c r="K94" s="36"/>
+      <c r="L94" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="M94" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="N94" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15">
+      <c r="A95" t="s">
+        <v>157</v>
+      </c>
+      <c r="B95" t="s">
+        <v>190</v>
+      </c>
+      <c r="C95" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D95" t="s">
+        <v>153</v>
+      </c>
+      <c r="G95" t="s">
+        <v>191</v>
+      </c>
+      <c r="H95" s="36">
+        <v>0</v>
+      </c>
+      <c r="I95" s="36">
+        <v>1</v>
+      </c>
+      <c r="J95" s="36"/>
+      <c r="K95" s="36"/>
+      <c r="L95" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="M95" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="N95" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15">
+      <c r="A96" t="s">
+        <v>180</v>
+      </c>
+      <c r="B96" t="s">
+        <v>193</v>
+      </c>
+      <c r="C96" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D96" t="s">
+        <v>153</v>
+      </c>
+      <c r="G96" t="s">
+        <v>194</v>
+      </c>
+      <c r="H96" s="36">
+        <v>0</v>
+      </c>
+      <c r="I96" s="36">
+        <v>1</v>
+      </c>
+      <c r="J96" s="36"/>
+      <c r="K96" s="36"/>
+      <c r="L96" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="M96" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="N96" t="s">
+        <v>195</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:P88" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:P95" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1 H2:I80 H89:I1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1 H89:I89 H2:I80 H97:I1048576">
       <formula1>"0,1"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C89 C2:C80 C97:C1048576">
+      <formula1>"临检,进院"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A80 A88:A1048576">
       <formula1>prod_name!$A:$A</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C80 C89:C1048576">
-      <formula1>"临检,进院"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D80 D87:D1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D80 D87:D94 D95:D96 D97:D1048576">
       <formula1>"定制,通用,通用-完整,通用-简版"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5897,37 +6189,37 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="B1" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="C1" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="D1" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="E1" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="F1" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="K1" s="30" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -5953,266 +6245,266 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="B2" s="29">
         <v>105</v>
       </c>
       <c r="C2" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="B3" s="29">
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B4" s="29">
         <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="B5" s="29">
         <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="B6" s="29">
         <v>150</v>
       </c>
       <c r="C6" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="B7" s="29">
         <v>150</v>
       </c>
       <c r="C7" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="B8" s="29">
         <v>150</v>
       </c>
       <c r="C8" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="B9" s="29">
         <v>180</v>
       </c>
       <c r="C9" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="B10" s="29">
         <v>180</v>
       </c>
       <c r="C10" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="B11" s="29">
         <v>180</v>
       </c>
       <c r="C11" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="B12" s="29">
         <v>180</v>
       </c>
       <c r="C12" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="B13" s="29">
         <v>180</v>
       </c>
       <c r="C13" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="B14" s="29">
         <v>180</v>
       </c>
       <c r="C14" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="B15" s="29">
         <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="B16" s="29">
         <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="B17" s="29">
         <v>120</v>
       </c>
       <c r="C17" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="B18" s="29">
         <v>120</v>
       </c>
       <c r="C18" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="B19" s="29">
         <v>120</v>
       </c>
       <c r="C19" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="B20" s="29">
         <v>150</v>
       </c>
       <c r="C20" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="B21" s="29">
         <v>150</v>
       </c>
       <c r="C21" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="B22" s="29">
         <v>150</v>
       </c>
       <c r="C22" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="B23" s="29">
         <v>150</v>
       </c>
       <c r="C23" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="B24" s="29">
         <v>150</v>
       </c>
       <c r="C24" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -6233,15 +6525,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="28" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>24</v>
@@ -6249,7 +6541,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="B3" t="s">
         <v>85</v>
@@ -6257,7 +6549,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="B4" t="s">
         <v>85</v>
@@ -6265,111 +6557,111 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="28" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="28" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="28" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="28" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="28" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="28" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="28" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="28" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="28" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="28" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="28" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="28" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="B17" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="28" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>63</v>
@@ -6377,7 +6669,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="28" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="B19" s="28" t="s">
         <v>63</v>
@@ -6385,15 +6677,15 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="28" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="28" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="B21" t="s">
         <v>85</v>
@@ -6401,23 +6693,23 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="28" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="28" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="B24" t="s">
         <v>157</v>
@@ -6425,7 +6717,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="28" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="B25" s="28" t="s">
         <v>36</v>
@@ -6433,18 +6725,18 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="28" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="28" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -6457,7 +6749,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A62"/>
+  <dimension ref="A1:A63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="29.8333333333333" customWidth="1"/>
@@ -6476,37 +6768,37 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -6516,17 +6808,17 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -6536,12 +6828,12 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -6556,77 +6848,77 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -6636,42 +6928,42 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="26" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
     </row>
     <row r="43" spans="1:1">
@@ -6681,17 +6973,17 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
     </row>
     <row r="47" spans="1:1">
@@ -6772,6 +7064,11 @@
     <row r="62" spans="1:1">
       <c r="A62" t="s">
         <v>172</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -6799,7 +7096,7 @@
   <sheetData>
     <row r="2" spans="1:2">
       <c r="A2" s="17" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -6807,7 +7104,7 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -6815,15 +7112,15 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="18" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="B5" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -6831,7 +7128,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -6839,7 +7136,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -6847,7 +7144,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -6855,7 +7152,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -6863,7 +7160,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -6871,7 +7168,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -6879,7 +7176,7 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6887,25 +7184,25 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="18" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="B14" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="19" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -6916,7 +7213,7 @@
         <v>2</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>4</v>
@@ -6943,7 +7240,7 @@
         <v>14</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
     </row>
     <row r="18" ht="15.5" spans="1:12">
@@ -6957,26 +7254,26 @@
         <v>19</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="G18" s="3">
         <v>0</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="L18" s="3"/>
     </row>
@@ -6993,22 +7290,22 @@
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="G19" s="3">
         <v>0</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="L19" s="3"/>
     </row>
@@ -7020,27 +7317,27 @@
         <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="L20" s="3"/>
     </row>
@@ -7055,28 +7352,28 @@
         <v>19</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="G21" s="3">
         <v>0</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="L21" s="3"/>
     </row>
@@ -7088,61 +7385,61 @@
         <v>148</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="L22" s="3"/>
     </row>
     <row r="25" ht="15.5" spans="1:12">
       <c r="A25" s="23" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
     </row>
     <row r="26" ht="15.5" spans="1:12">
       <c r="A26" s="24" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
     </row>
     <row r="27" ht="15.5" spans="1:12">
       <c r="A27" s="23" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="B27" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
     </row>
     <row r="28" ht="15.5" spans="1:12">
       <c r="A28" s="23" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="B28" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
     </row>
     <row r="29" ht="15.5" spans="1:12">
       <c r="A29" s="25" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="B29" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
     </row>
     <row r="30" ht="15.5" spans="1:12">
@@ -7150,7 +7447,7 @@
         <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -7179,16 +7476,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="13" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>14</v>
@@ -7199,78 +7496,78 @@
         <v>19</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="15"/>
       <c r="B3" s="3" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="14" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="16"/>
       <c r="B5" s="3" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="15"/>
       <c r="B6" s="3" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -7292,79 +7589,79 @@
   <sheetData>
     <row r="5" spans="3:6">
       <c r="C5" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="D5" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" spans="3:6">
       <c r="C7" s="1" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8" spans="3:6">
       <c r="C8" s="2" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
     <row r="9" spans="3:6">
       <c r="C9" s="2" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="3:6">
       <c r="C10" s="4" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" spans="3:6">
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="3" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12" spans="3:6">
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="3" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13" spans="3:6">
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="3" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
     </row>
     <row r="14" spans="3:6">
@@ -7375,23 +7672,23 @@
     </row>
     <row r="15" spans="3:6">
       <c r="C15" s="4" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="3:6">
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="3" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="F16" s="3"/>
     </row>
@@ -7399,7 +7696,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="3" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="F17" s="3"/>
     </row>
@@ -7407,7 +7704,7 @@
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="3" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="F18" s="3"/>
     </row>
@@ -7415,7 +7712,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="3" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="F19" s="3"/>
     </row>
@@ -7423,19 +7720,19 @@
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="3" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="F20" s="3"/>
     </row>
     <row r="21" spans="3:6">
       <c r="C21" s="4" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="F21" s="3"/>
     </row>
@@ -7443,7 +7740,7 @@
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="3" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="F22" s="3"/>
     </row>
@@ -7451,13 +7748,13 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="3" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="F23" s="3"/>
     </row>
     <row r="24" spans="3:6">
       <c r="C24" s="3" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>14</v>
@@ -7467,17 +7764,17 @@
     </row>
     <row r="25" spans="3:6">
       <c r="C25" s="3" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
     </row>
     <row r="26" spans="3:6">
       <c r="C26" s="3" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="3"/>
@@ -7485,7 +7782,7 @@
     </row>
     <row r="27" spans="3:6">
       <c r="C27" s="3" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="D27" s="7"/>
       <c r="E27" s="3"/>
@@ -7493,7 +7790,7 @@
     </row>
     <row r="28" spans="3:6">
       <c r="C28" s="3" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="3"/>
@@ -7501,7 +7798,7 @@
     </row>
     <row r="29" spans="3:6">
       <c r="C29" s="3" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="3"/>
@@ -7509,19 +7806,19 @@
     </row>
     <row r="35" spans="3:6">
       <c r="C35" s="9" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="F35" s="9"/>
     </row>
     <row r="36" spans="3:6">
       <c r="C36" s="11" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
@@ -7529,29 +7826,29 @@
     </row>
     <row r="37" spans="3:6">
       <c r="C37" s="12" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="E37" s="12"/>
       <c r="F37" s="9"/>
     </row>
     <row r="38" spans="3:6">
       <c r="C38" s="12" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="F38" s="9"/>
     </row>
     <row r="39" spans="3:6">
       <c r="C39" s="12" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="D39" s="12" t="s">
         <v>14</v>
